--- a/Excel/EquipStrengthFeeConfig.xlsx
+++ b/Excel/EquipStrengthFeeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1001,8 +1001,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XER37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:XER39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
@@ -1029,7 +1029,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1045,7 +1045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1061,7 +1061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1077,7 +1077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:16372">
+    <row r="6" customFormat="1" ht="14" spans="1:16372">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -1095,14 +1095,14 @@
       <c r="XEQ6" s="2"/>
       <c r="XER6" s="2"/>
     </row>
-    <row r="7" customFormat="1" spans="1:16372">
+    <row r="7" customFormat="1" ht="14" spans="1:16372">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:D37" si="0">E6+1</f>
+        <f t="shared" ref="D7:D39" si="0">E6+1</f>
         <v>101</v>
       </c>
       <c r="E7" s="2">
@@ -1114,7 +1114,7 @@
       <c r="XEQ7" s="2"/>
       <c r="XER7" s="2"/>
     </row>
-    <row r="8" customFormat="1" spans="1:16372">
+    <row r="8" customFormat="1" ht="14" spans="1:16372">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -1133,7 +1133,7 @@
       <c r="XEQ8" s="2"/>
       <c r="XER8" s="2"/>
     </row>
-    <row r="9" customFormat="1" spans="1:16372">
+    <row r="9" customFormat="1" ht="14" spans="1:16372">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -1152,7 +1152,7 @@
       <c r="XEQ9" s="2"/>
       <c r="XER9" s="2"/>
     </row>
-    <row r="10" customFormat="1" spans="1:16372">
+    <row r="10" customFormat="1" ht="14" spans="1:16372">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -1171,7 +1171,7 @@
       <c r="XEQ10" s="2"/>
       <c r="XER10" s="2"/>
     </row>
-    <row r="11" customFormat="1" spans="1:16372">
+    <row r="11" customFormat="1" ht="14" spans="1:16372">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -1190,7 +1190,7 @@
       <c r="XEQ11" s="2"/>
       <c r="XER11" s="2"/>
     </row>
-    <row r="12" customFormat="1" spans="1:16372">
+    <row r="12" customFormat="1" ht="14" spans="1:16372">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -1209,7 +1209,7 @@
       <c r="XEQ12" s="2"/>
       <c r="XER12" s="2"/>
     </row>
-    <row r="13" customFormat="1" spans="1:16372">
+    <row r="13" customFormat="1" ht="14" spans="1:16372">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -1228,7 +1228,7 @@
       <c r="XEQ13" s="2"/>
       <c r="XER13" s="2"/>
     </row>
-    <row r="14" customFormat="1" spans="1:16372">
+    <row r="14" customFormat="1" ht="14" spans="1:16372">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2">
@@ -1247,7 +1247,7 @@
       <c r="XEQ14" s="2"/>
       <c r="XER14" s="2"/>
     </row>
-    <row r="15" customFormat="1" spans="1:16372">
+    <row r="15" customFormat="1" ht="14" spans="1:16372">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2">
@@ -1266,7 +1266,7 @@
       <c r="XEQ15" s="2"/>
       <c r="XER15" s="2"/>
     </row>
-    <row r="16" customFormat="1" spans="1:16372">
+    <row r="16" customFormat="1" ht="14" spans="1:16372">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2">
@@ -1285,7 +1285,7 @@
       <c r="XEQ16" s="2"/>
       <c r="XER16" s="2"/>
     </row>
-    <row r="17" customFormat="1" spans="1:16372">
+    <row r="17" customFormat="1" ht="14" spans="1:16372">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2">
@@ -1304,7 +1304,7 @@
       <c r="XEQ17" s="2"/>
       <c r="XER17" s="2"/>
     </row>
-    <row r="18" customFormat="1" spans="1:16372">
+    <row r="18" customFormat="1" ht="14" spans="1:16372">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2">
@@ -1323,7 +1323,7 @@
       <c r="XEQ18" s="2"/>
       <c r="XER18" s="2"/>
     </row>
-    <row r="19" customFormat="1" spans="1:16372">
+    <row r="19" customFormat="1" ht="14" spans="1:16372">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2">
@@ -1342,7 +1342,7 @@
       <c r="XEQ19" s="2"/>
       <c r="XER19" s="2"/>
     </row>
-    <row r="20" customFormat="1" spans="1:16372">
+    <row r="20" customFormat="1" ht="14" spans="1:16372">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2">
@@ -1361,7 +1361,7 @@
       <c r="XEQ20" s="2"/>
       <c r="XER20" s="2"/>
     </row>
-    <row r="21" customFormat="1" spans="1:16372">
+    <row r="21" customFormat="1" ht="14" spans="1:16372">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2">
@@ -1380,7 +1380,7 @@
       <c r="XEQ21" s="2"/>
       <c r="XER21" s="2"/>
     </row>
-    <row r="22" customFormat="1" spans="1:16372">
+    <row r="22" customFormat="1" ht="14" spans="1:16372">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2">
@@ -1399,7 +1399,7 @@
       <c r="XEQ22" s="2"/>
       <c r="XER22" s="2"/>
     </row>
-    <row r="23" customFormat="1" spans="1:16372">
+    <row r="23" customFormat="1" ht="14" spans="1:16372">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2">
@@ -1418,7 +1418,7 @@
       <c r="XEQ23" s="2"/>
       <c r="XER23" s="2"/>
     </row>
-    <row r="24" customFormat="1" spans="1:16372">
+    <row r="24" customFormat="1" ht="14" spans="1:16372">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
@@ -1437,7 +1437,7 @@
       <c r="XEQ24" s="2"/>
       <c r="XER24" s="2"/>
     </row>
-    <row r="25" customFormat="1" spans="1:16372">
+    <row r="25" customFormat="1" ht="14" spans="1:16372">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2">
@@ -1456,7 +1456,7 @@
       <c r="XEQ25" s="2"/>
       <c r="XER25" s="2"/>
     </row>
-    <row r="26" customFormat="1" spans="1:16372">
+    <row r="26" customFormat="1" ht="14" spans="1:16372">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2">
@@ -1475,7 +1475,7 @@
       <c r="XEQ26" s="2"/>
       <c r="XER26" s="2"/>
     </row>
-    <row r="27" spans="3:7">
+    <row r="27" ht="14" spans="3:7">
       <c r="C27" s="2">
         <v>22</v>
       </c>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G27"/>
     </row>
-    <row r="28" spans="3:7">
+    <row r="28" ht="14" spans="3:7">
       <c r="C28" s="2">
         <v>23</v>
       </c>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G28"/>
     </row>
-    <row r="29" spans="3:7">
+    <row r="29" ht="14" spans="3:7">
       <c r="C29" s="2">
         <v>24</v>
       </c>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G29"/>
     </row>
-    <row r="30" spans="3:7">
+    <row r="30" ht="14" spans="3:7">
       <c r="C30" s="2">
         <v>25</v>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G30"/>
     </row>
-    <row r="31" spans="3:7">
+    <row r="31" ht="14" spans="3:7">
       <c r="C31" s="2">
         <v>26</v>
       </c>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="G31"/>
     </row>
-    <row r="32" spans="3:7">
+    <row r="32" ht="14" spans="3:7">
       <c r="C32" s="2">
         <v>27</v>
       </c>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G32"/>
     </row>
-    <row r="33" spans="3:7">
+    <row r="33" ht="14" spans="3:7">
       <c r="C33" s="2">
         <v>28</v>
       </c>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G33"/>
     </row>
-    <row r="34" spans="3:7">
+    <row r="34" ht="14" spans="3:7">
       <c r="C34" s="2">
         <v>29</v>
       </c>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G34"/>
     </row>
-    <row r="35" spans="3:7">
+    <row r="35" ht="14" spans="3:7">
       <c r="C35" s="2">
         <v>30</v>
       </c>
@@ -1647,6 +1647,36 @@
       </c>
       <c r="F37" s="2">
         <v>12000</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6">
+      <c r="C38" s="2">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="0"/>
+        <v>500001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="F38" s="2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6">
+      <c r="C39" s="2">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="0"/>
+        <v>1000001</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F39" s="2">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
